--- a/luva.xlsx
+++ b/luva.xlsx
@@ -22,16 +22,13 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -432,41 +420,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>الوقت</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الوردية</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>المشرف</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>نوع البالة</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>وزن البالة</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
@@ -491,7 +479,7 @@
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,7 +508,7 @@
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -549,7 +537,7 @@
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -578,7 +566,7 @@
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +595,7 @@
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -636,7 +624,7 @@
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -665,7 +653,7 @@
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -694,7 +682,7 @@
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,7 +711,7 @@
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -752,7 +740,7 @@
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -781,7 +769,7 @@
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -810,7 +798,7 @@
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -839,7 +827,7 @@
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -868,7 +856,7 @@
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -897,7 +885,7 @@
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -926,7 +914,7 @@
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -955,7 +943,7 @@
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -984,7 +972,7 @@
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1013,7 +1001,7 @@
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1042,7 +1030,7 @@
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1071,7 +1059,7 @@
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1100,7 +1088,7 @@
       <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1129,7 +1117,7 @@
       <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1158,7 +1146,7 @@
       <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1187,7 +1175,7 @@
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1216,7 +1204,7 @@
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1245,7 +1233,7 @@
       <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1274,7 +1262,7 @@
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1303,7 +1291,7 @@
       <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1332,7 +1320,7 @@
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1361,7 +1349,7 @@
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1390,7 +1378,7 @@
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1419,7 +1407,7 @@
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1448,7 +1436,7 @@
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1477,7 +1465,7 @@
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1506,7 +1494,7 @@
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1535,7 +1523,7 @@
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1564,7 +1552,7 @@
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1593,7 +1581,7 @@
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1622,7 +1610,7 @@
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1651,7 +1639,7 @@
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1680,7 +1668,7 @@
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1709,7 +1697,7 @@
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1736,6 +1724,267 @@
         <v>0.005</v>
       </c>
       <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:10:56.142060</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>800</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:11:08.577356</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>80</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:11:17.993556</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:11:24.930739</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:11:38.061672</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:15:33.020431</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:15:47.516322</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:15:54.959303</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:19:55.663549</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>برم</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,7 +1958,7 @@
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -1985,6 +1985,35 @@
         <v>0.1</v>
       </c>
       <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>07:35:13.458327</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>اسطبات تدویر</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1987,7 +1987,7 @@
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2014,6 +2014,39 @@
         <v>0.1</v>
       </c>
       <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>08:19:29.236484</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ay طلومةب حاليكو حواين Wh j Tee Sates a ee Y مجع eee سما ) 05885 مهما 5-95 تنيت أستهو يج1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2016,7 +2016,7 @@
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2047,6 +2047,35 @@
           <t>ay طلومةب حاليكو حواين Wh j Tee Sates a ee Y مجع eee سما ) 05885 مهما 5-95 تنيت أستهو يج1</t>
         </is>
       </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19:13:10.500949</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2076,6 +2076,35 @@
         <v>0.5</v>
       </c>
       <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19:13:14.803440</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2078,7 +2078,7 @@
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2105,6 +2105,35 @@
         <v>0.5</v>
       </c>
       <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>19:13:19.286580</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2107,7 +2107,7 @@
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2134,6 +2134,35 @@
         <v>0.6</v>
       </c>
       <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>14:26:06.480420</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>5555</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,7 +2136,7 @@
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2163,6 +2163,35 @@
         <v>5555</v>
       </c>
       <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>14:26:25.435990</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>5555</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,7 +2165,7 @@
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2192,6 +2192,35 @@
         <v>5555</v>
       </c>
       <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>19:08:44.665640</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>555</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +2194,7 @@
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2221,6 +2221,35 @@
         <v>555</v>
       </c>
       <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19:08:54.868090</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>برم انفاق</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>555</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,7 +2223,7 @@
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2250,6 +2250,35 @@
         <v>555</v>
       </c>
       <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>19:09:05.234320</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>555</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,7 +2252,7 @@
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2279,6 +2279,35 @@
         <v>555</v>
       </c>
       <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>19:17:20.416430</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>666</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,7 +2281,7 @@
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2308,6 +2308,35 @@
         <v>666</v>
       </c>
       <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>19:17:26.936546</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>انسT.A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>666</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2310,7 +2310,7 @@
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2337,6 +2337,35 @@
         <v>666</v>
       </c>
       <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>05:53:39.365598</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>كرد</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1432</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,7 +2339,7 @@
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2366,6 +2366,35 @@
         <v>1432</v>
       </c>
       <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>05:54:22.189091</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2664</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2368,7 +2368,7 @@
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2395,6 +2395,35 @@
         <v>2664</v>
       </c>
       <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>05:54:42.987686</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>177</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,7 +2397,7 @@
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2424,6 +2424,35 @@
         <v>177</v>
       </c>
       <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>05:55:10.205463</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>شرق الغزل</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>200</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2426,7 +2426,7 @@
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2453,6 +2453,35 @@
         <v>200</v>
       </c>
       <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>05:55:57.644684</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>210</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2455,7 +2455,7 @@
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2482,6 +2482,35 @@
         <v>210</v>
       </c>
       <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>05:56:15.918660</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>198</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,7 +2484,7 @@
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2511,6 +2511,35 @@
         <v>198</v>
       </c>
       <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>05:56:32.850175</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>150</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2513,7 +2513,7 @@
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2540,6 +2540,35 @@
         <v>150</v>
       </c>
       <c r="G74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>05:56:56.415964</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>قماش</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>202</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2542,7 +2542,7 @@
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2569,6 +2569,35 @@
         <v>202</v>
       </c>
       <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>05:57:52.402494</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>شرق الغزل</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>210</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2571,7 +2571,7 @@
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2598,6 +2598,35 @@
         <v>210</v>
       </c>
       <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>05:58:23.366238</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>347</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2600,7 +2600,7 @@
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2627,6 +2627,35 @@
         <v>347</v>
       </c>
       <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>05:58:48.795389</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>كرد</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1198</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,7 +2629,7 @@
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>46214</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -2656,6 +2656,35 @@
         <v>1198</v>
       </c>
       <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>05:59:08.380584</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2691</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
